--- a/data/trending_integrated_20260907_14.xlsx
+++ b/data/trending_integrated_20260907_14.xlsx
@@ -581,10 +581,10 @@
         <v>799</v>
       </c>
       <c r="F2" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G2" t="n">
-        <v>1313</v>
+        <v>1344</v>
       </c>
       <c r="H2" t="n">
         <v>0.16</v>
@@ -610,7 +610,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>779537095125</v>
+        <v>779882249025</v>
       </c>
       <c r="P2" t="n">
         <v>30550</v>
@@ -619,23 +619,23 @@
         <v>8200</v>
       </c>
       <c r="R2" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="S2" t="n">
         <v>-1000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>세계 최초 반지 혈압계 기술력과 건강보험 급여 등재 관련 뉴스를 기반으로 한 강한 상승 기대감.</t>
+          <t>‘CART 혈압계’의 건강보험 급여 등재 및 세계 최초 반지 혈압계 기술력에 기반한 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['반지 혈압계', '건강보험 급여', '세계 최초']</t>
+          <t>['CART 혈압계', '건강보험 급여', '세계 최초']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10080</v>
+        <v>10070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+20.72%</t>
+          <t>+20.60%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="F3" t="n">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>136695787280</v>
+        <v>147600024660</v>
       </c>
       <c r="P3" t="n">
         <v>20850</v>
@@ -711,23 +711,23 @@
         <v>4020</v>
       </c>
       <c r="R3" t="n">
-        <v>100000</v>
+        <v>54000</v>
       </c>
       <c r="S3" t="n">
-        <v>-232000</v>
+        <v>-937000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>일론 머스크 관련 뉴스 및 두산에너빌리티 연관성을 바탕으로 한 강한 상승 기대감, 기술적 재료 언급.</t>
+          <t>삼미금속, 미국 초대형 가스발전 열병합 사업 수주 뉴스로 급등. 테마 기대감 형성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['일론 머스크', '두산에너빌리티', '가스터빈']</t>
+          <t>['가스터빈', '가스발전', '테마']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -762,13 +762,13 @@
         <v>0.37</v>
       </c>
       <c r="E4" t="n">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="F4" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>193</v>
+        <v>228</v>
       </c>
       <c r="H4" t="n">
         <v>1.08</v>
@@ -794,7 +794,7 @@
         <v>0.71</v>
       </c>
       <c r="O4" t="n">
-        <v>107134387535</v>
+        <v>119482542980</v>
       </c>
       <c r="P4" t="n">
         <v>34650</v>
@@ -803,23 +803,23 @@
         <v>6980</v>
       </c>
       <c r="R4" t="n">
-        <v>-36000</v>
+        <v>-29000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>스카이랩스와의 비교 및 저평가 논리를 바탕으로 한 급등 기대감, 공모가 대비 높은 상승 잠재력 언급.</t>
+          <t>레메디, 기술력 부각 및 공모가 대비 저평가 논란 속 18500원 돌파 시도. 텐배거 기대감 형성.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['저평가', '공모가', '텐배거']</t>
+          <t>['기술력', '저평가', '공모가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9510</v>
+        <v>9460</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+16.26%</t>
+          <t>+15.65%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.44</v>
       </c>
       <c r="E5" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="H5" t="n">
         <v>1.58</v>
@@ -886,7 +886,7 @@
         <v>1.14</v>
       </c>
       <c r="O5" t="n">
-        <v>88725666105</v>
+        <v>92171434740</v>
       </c>
       <c r="P5" t="n">
         <v>22500</v>
@@ -895,23 +895,23 @@
         <v>4560</v>
       </c>
       <c r="R5" t="n">
-        <v>152000</v>
+        <v>146000</v>
       </c>
       <c r="S5" t="n">
         <v>-9000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외인 프로그램 매수 등장과 함께 10000원 안착 및 신고가 돌파에 대한 기대감, 추세 분석.</t>
+          <t>매드업, AI 관련 뉴스 및 외인 프로그램 매수 유입으로 10000원 안착 시도. 신고가 기대감.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외인 매수', '신고가', '추세 분석']</t>
+          <t>['AI', '외인 프로그램 매수', '신고가']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50400</v>
+        <v>50600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+14.94%</t>
+          <t>+15.39%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.47</v>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>701</v>
+        <v>156</v>
       </c>
       <c r="H6" t="n">
         <v>14.18</v>
@@ -978,7 +978,7 @@
         <v>13.71</v>
       </c>
       <c r="O6" t="n">
-        <v>153406524325</v>
+        <v>158352557825</v>
       </c>
       <c r="P6" t="n">
         <v>108900</v>
@@ -987,10 +987,10 @@
         <v>18230</v>
       </c>
       <c r="R6" t="n">
-        <v>156000</v>
+        <v>170000</v>
       </c>
       <c r="S6" t="n">
-        <v>-11000</v>
+        <v>-46000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>JW신약</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3580</v>
+        <v>6490</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+9.65%</t>
+          <t>+10.94%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.52</v>
+        <v>-0.7</v>
       </c>
       <c r="E7" t="n">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>268</v>
+        <v>570</v>
       </c>
       <c r="H7" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,60 +1055,60 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3265</v>
+        <v>5850</v>
       </c>
       <c r="K7" t="n">
-        <v>3200</v>
+        <v>6000</v>
       </c>
       <c r="L7" t="n">
-        <v>3900</v>
+        <v>6550</v>
       </c>
       <c r="M7" t="n">
-        <v>3185</v>
+        <v>5940</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="O7" t="n">
-        <v>193321474153</v>
+        <v>16600447335</v>
       </c>
       <c r="P7" t="n">
-        <v>3900</v>
+        <v>21500</v>
       </c>
       <c r="Q7" t="n">
-        <v>1246</v>
+        <v>2300</v>
       </c>
       <c r="R7" t="n">
-        <v>-840000</v>
+        <v>13000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>긍정적인 단기 수익 언급과 함께 장기 투자 가능성을 질문하는 내용, 투자 경고에 대한 언급.</t>
+          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단기 수익', '장기 투자', '투자 경고']</t>
+          <t>['임상 2a', '폐암학회', '6500원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>067290</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86300</v>
+        <v>87100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+8.96%</t>
+          <t>+9.97%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>320</v>
+        <v>184</v>
       </c>
       <c r="F8" t="n">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="G8" t="n">
-        <v>1299</v>
+        <v>666</v>
       </c>
       <c r="H8" t="n">
         <v>23.53</v>
@@ -1162,7 +1162,7 @@
         <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>366978024550</v>
+        <v>408197486350</v>
       </c>
       <c r="P8" t="n">
         <v>139200</v>
@@ -1171,23 +1171,23 @@
         <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>519000</v>
+        <v>540000</v>
       </c>
       <c r="S8" t="n">
-        <v>107000</v>
+        <v>169000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>일론 머스크 관련 뉴스와 대규모 투자 소식을 기반으로 한 긍정적인 전망.</t>
+          <t>두산에너빌리티, 일론 머스크 관련 복합화력발전소 뉴스 주목. 외인 매수세 유입되며 상승 기대감 고조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['일론 머스크', '대미 투자', '가스복합']</t>
+          <t>['복합화력발전소', '일론 머스크', '외인 매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1207,31 +1207,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6320</v>
+        <v>3580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+8.03%</t>
+          <t>+9.65%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.7</v>
+        <v>-0.52</v>
       </c>
       <c r="E9" t="n">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="F9" t="n">
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="G9" t="n">
-        <v>548</v>
+        <v>288</v>
       </c>
       <c r="H9" t="n">
-        <v>1.61</v>
+        <v>1.25</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,60 +1239,60 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>5850</v>
+        <v>3265</v>
       </c>
       <c r="K9" t="n">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="L9" t="n">
-        <v>6550</v>
+        <v>3900</v>
       </c>
       <c r="M9" t="n">
-        <v>5940</v>
+        <v>3185</v>
       </c>
       <c r="N9" t="n">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="O9" t="n">
-        <v>15977173930</v>
+        <v>195981206566</v>
       </c>
       <c r="P9" t="n">
-        <v>21500</v>
+        <v>3900</v>
       </c>
       <c r="Q9" t="n">
-        <v>2300</v>
+        <v>1246</v>
       </c>
       <c r="R9" t="n">
-        <v>-8000</v>
+        <v>-1196000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>페니트리움바이오, 임상 2a 결과 발표 및 세계폐암학회 참가 예정으로 인한 기대감 형성. 6500원 돌파 시 추가 상승 전망.</t>
+          <t>JW신약, 탈모 치료제 관련 언급 있으나 투자 주의 필요. 단기 수익 관찰.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['임상 2a', '폐암학회', '6500원']</t>
+          <t>['탈모', '투자 주의', '단기 수익']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1764000</v>
+        <v>1768000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+7.10%</t>
+          <t>+7.35%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.05</v>
       </c>
       <c r="E10" t="n">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="F10" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G10" t="n">
-        <v>2597</v>
+        <v>2637</v>
       </c>
       <c r="H10" t="n">
         <v>50.5</v>
@@ -1346,7 +1346,7 @@
         <v>50.45</v>
       </c>
       <c r="O10" t="n">
-        <v>4385237957000</v>
+        <v>4743944213000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1355,23 +1355,23 @@
         <v>274000</v>
       </c>
       <c r="R10" t="n">
-        <v>479000</v>
+        <v>537000</v>
       </c>
       <c r="S10" t="n">
-        <v>203000</v>
+        <v>243000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>메모리 재고 감소 및 2차 상승 시작 기대감, 외인/기관 매수 확대에 따른 긍정적 전망.</t>
+          <t>SK하이닉스, 메모리 시장 2차 상승 기대감 속 180만원 돌파 시도. 외인 및 기관 매수 확대 관찰.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['메모리 재고', '외인 매수', '기술적 분석']</t>
+          <t>['메모리', '외인 매수', '기관 매수']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>214500</v>
+        <v>215500</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+6.45%</t>
+          <t>+6.95%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.05</v>
       </c>
       <c r="E11" t="n">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="F11" t="n">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="G11" t="n">
-        <v>1430</v>
+        <v>1456</v>
       </c>
       <c r="H11" t="n">
         <v>29.46</v>
@@ -1438,7 +1438,7 @@
         <v>29.51</v>
       </c>
       <c r="O11" t="n">
-        <v>328638040750</v>
+        <v>337800402250</v>
       </c>
       <c r="P11" t="n">
         <v>438000</v>
@@ -1447,23 +1447,23 @@
         <v>74700</v>
       </c>
       <c r="R11" t="n">
-        <v>306000</v>
+        <v>311000</v>
       </c>
       <c r="S11" t="n">
-        <v>133000</v>
+        <v>140000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>CES 2024 관련 호재와 함께 100만원 목표주가 제시. 빅테크와의 액추에이터 수주 협의 중 소식.</t>
+          <t>모간의 공매도 및 숏커버, LG전자 모터 기술의 로봇 관절 적용 등 호재에 따른 급등세.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['CES', '액추에이터', '수주']</t>
+          <t>['공매도', '숏커버', '로봇 관절']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17880</v>
+        <v>17970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+6.11%</t>
+          <t>+6.65%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0.04</v>
       </c>
       <c r="E12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G12" t="n">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="H12" t="n">
         <v>10.4</v>
@@ -1530,7 +1530,7 @@
         <v>10.36</v>
       </c>
       <c r="O12" t="n">
-        <v>110729083955</v>
+        <v>117385246150</v>
       </c>
       <c r="P12" t="n">
         <v>40350</v>
@@ -1539,10 +1539,10 @@
         <v>3320</v>
       </c>
       <c r="R12" t="n">
-        <v>340000</v>
+        <v>330000</v>
       </c>
       <c r="S12" t="n">
-        <v>24000</v>
+        <v>39000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1575,31 +1575,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>267750</v>
+        <v>8460</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>+4.79%</t>
+          <t>+6.42%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.02</v>
+        <v>-0.72</v>
       </c>
       <c r="E13" t="n">
-        <v>795</v>
+        <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>423</v>
+        <v>56</v>
       </c>
       <c r="G13" t="n">
-        <v>2152</v>
+        <v>174</v>
       </c>
       <c r="H13" t="n">
-        <v>46.73</v>
+        <v>0.6</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>255500</v>
+        <v>7950</v>
       </c>
       <c r="K13" t="n">
-        <v>267000</v>
+        <v>8200</v>
       </c>
       <c r="L13" t="n">
-        <v>269000</v>
+        <v>9210</v>
       </c>
       <c r="M13" t="n">
-        <v>264000</v>
+        <v>7980</v>
       </c>
       <c r="N13" t="n">
-        <v>46.71</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>3261256177250</v>
+        <v>98044573210</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>15960</v>
       </c>
       <c r="Q13" t="n">
-        <v>69600</v>
+        <v>3500</v>
       </c>
       <c r="R13" t="n">
-        <v>1309000</v>
+        <v>-10000</v>
       </c>
       <c r="S13" t="n">
-        <v>1097000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 언급과 개인적인 희망사항이 혼재된 게시글들로, 객관적인 분석 근거 부족.</t>
+          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,51 +1647,51 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['미프진', '거래량', '수급']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>현대약품</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8300</v>
+        <v>268750</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>+4.40%</t>
+          <t>+5.19%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.72</v>
+        <v>0.02</v>
       </c>
       <c r="E14" t="n">
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="F14" t="n">
-        <v>56</v>
+        <v>360</v>
       </c>
       <c r="G14" t="n">
-        <v>179</v>
+        <v>1669</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6</v>
+        <v>46.73</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,60 +1699,60 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>7950</v>
+        <v>255500</v>
       </c>
       <c r="K14" t="n">
-        <v>8200</v>
+        <v>267000</v>
       </c>
       <c r="L14" t="n">
-        <v>9210</v>
+        <v>269500</v>
       </c>
       <c r="M14" t="n">
-        <v>7980</v>
+        <v>264000</v>
       </c>
       <c r="N14" t="n">
-        <v>1.32</v>
+        <v>46.71</v>
       </c>
       <c r="O14" t="n">
-        <v>96018536220</v>
+        <v>3705990040750</v>
       </c>
       <c r="P14" t="n">
-        <v>15960</v>
+        <v>374500</v>
       </c>
       <c r="Q14" t="n">
-        <v>3500</v>
+        <v>69600</v>
       </c>
       <c r="R14" t="n">
-        <v>26000</v>
+        <v>1534000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1290000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미프진 관련 기대감 및 거래량 증가 속 가격 변동성 확대. 긍정적 수급 기대.</t>
+          <t>삼성전자, 기술적 반등 및 자사주 매입 기대감 속 27만원 돌파 시도. 개미 매도세 관찰.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['미프진', '거래량', '수급']</t>
+          <t>['자사주 매입', '기술적 반등', '반도체']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>004310</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13410</v>
+        <v>13430</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3.07%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.09</v>
       </c>
       <c r="E15" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F15" t="n">
         <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="H15" t="n">
         <v>1.82</v>
@@ -1806,7 +1806,7 @@
         <v>1.91</v>
       </c>
       <c r="O15" t="n">
-        <v>73940319390</v>
+        <v>76100674165</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1815,7 +1815,7 @@
         <v>1252</v>
       </c>
       <c r="R15" t="n">
-        <v>336000</v>
+        <v>312000</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5870</v>
+        <v>5780</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>+2.26%</t>
+          <t>+0.70%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="F16" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G16" t="n">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1898,7 +1898,7 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>17210590800</v>
+        <v>17988951265</v>
       </c>
       <c r="P16" t="n">
         <v>9680</v>
@@ -1907,23 +1907,23 @@
         <v>371</v>
       </c>
       <c r="R16" t="n">
-        <v>-5000</v>
+        <v>-1000</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>유증 및 전환사채 납입 완료 호재에도 불구하고, 반기 보고서 제출 지연 및 악재성 기사로 인한 하락 우려.</t>
+          <t>계약금, 유증, 전환사채 납입 완료에도 불구하고 반기보고서 지연 및 악재 뉴스 발생.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['유증', '반기 보고서', '악재']</t>
+          <t>['반기보고서', '유증', '악재']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>한화머시너리앤서비스홀딩스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6740</v>
+        <v>30300</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>+0.45%</t>
+          <t>+0.33%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.85</v>
+        <v>0.4</v>
       </c>
       <c r="E17" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="F17" t="n">
         <v>39</v>
       </c>
       <c r="G17" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="H17" t="n">
-        <v>16.4</v>
+        <v>49.01</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,38 +1975,38 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>6710</v>
+        <v>30200</v>
       </c>
       <c r="K17" t="n">
-        <v>6680</v>
+        <v>30350</v>
       </c>
       <c r="L17" t="n">
-        <v>7040</v>
+        <v>30900</v>
       </c>
       <c r="M17" t="n">
-        <v>6600</v>
+        <v>29900</v>
       </c>
       <c r="N17" t="n">
-        <v>15.55</v>
+        <v>24.02</v>
       </c>
       <c r="O17" t="n">
-        <v>12217773245</v>
+        <v>83722516150</v>
       </c>
       <c r="P17" t="n">
-        <v>13000</v>
+        <v>31200</v>
       </c>
       <c r="Q17" t="n">
-        <v>6030</v>
+        <v>21000</v>
       </c>
       <c r="R17" t="n">
-        <v>-57000</v>
+        <v>541000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>161000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
+          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['공매도', 'IPO', '모건스탠리']</t>
+          <t>['환율', '반도체', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,38 +2028,38 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0220W0</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한화머시너리앤서비스홀딩스</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30300</v>
+        <v>6730</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.4</v>
+        <v>0.85</v>
       </c>
       <c r="E18" t="n">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="H18" t="n">
-        <v>48.99</v>
+        <v>16.4</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,38 +2067,38 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>30200</v>
+        <v>6710</v>
       </c>
       <c r="K18" t="n">
-        <v>30350</v>
+        <v>6680</v>
       </c>
       <c r="L18" t="n">
-        <v>30900</v>
+        <v>7040</v>
       </c>
       <c r="M18" t="n">
-        <v>29900</v>
+        <v>6600</v>
       </c>
       <c r="N18" t="n">
-        <v>24.02</v>
+        <v>15.55</v>
       </c>
       <c r="O18" t="n">
-        <v>79874130900</v>
+        <v>12625851420</v>
       </c>
       <c r="P18" t="n">
-        <v>31200</v>
+        <v>13000</v>
       </c>
       <c r="Q18" t="n">
-        <v>21000</v>
+        <v>6030</v>
       </c>
       <c r="R18" t="n">
-        <v>481000</v>
+        <v>-65000</v>
       </c>
       <c r="S18" t="n">
-        <v>113000</v>
+        <v>-1000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>환율 하락 및 반도체 운송 수요 증가 기대. 3만원 구간 지지 및 4만원 목표. 공매도 숏커버링 가능성.</t>
+          <t>공매도 및 모건스탠리 매도 의혹 제기. 2차 폭락 및 개미 투자자 유입 시 하락 전망. IPO 예정 종목(한화세미텍, 한화로보틱스) 언급.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['환율', '반도체', '공매도']</t>
+          <t>['공매도', 'IPO', '모건스탠리']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,77 +2120,77 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>0220W0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16090</v>
+        <v>22550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E19" t="n">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="F19" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G19" t="n">
-        <v>520</v>
+        <v>214</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K19" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L19" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M19" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O19" t="n">
-        <v>42148599715</v>
+        <v>133127809550</v>
       </c>
       <c r="P19" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q19" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R19" t="n">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
+          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,11 +2199,11 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', '산단', '주가']</t>
+          <t>['로봇주', '신사업', '2연상']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,77 +2212,77 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22350</v>
+        <v>16110</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>79</v>
+        <v>109</v>
       </c>
       <c r="F20" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="G20" t="n">
-        <v>200</v>
+        <v>560</v>
       </c>
       <c r="H20" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>22500</v>
+        <v>16090</v>
       </c>
       <c r="K20" t="n">
-        <v>23100</v>
+        <v>16150</v>
       </c>
       <c r="L20" t="n">
-        <v>24000</v>
+        <v>16480</v>
       </c>
       <c r="M20" t="n">
-        <v>21500</v>
+        <v>15830</v>
       </c>
       <c r="N20" t="n">
-        <v>4.98</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>131733327025</v>
+        <v>43998164990</v>
       </c>
       <c r="P20" t="n">
-        <v>50600</v>
+        <v>19380</v>
       </c>
       <c r="Q20" t="n">
-        <v>9070</v>
+        <v>3200</v>
       </c>
       <c r="R20" t="n">
-        <v>9000</v>
+        <v>72000</v>
       </c>
       <c r="S20" t="n">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>로봇주 강세 및 신사업 진출 기대감. 2연상 및 23,800원 매수가.</t>
+          <t>금호건설, 반도체 산업 연관 가능성 언급에도 불구하고 주가 부진 및 차트 하향 추세 관찰. 투자 심리 불확실.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,11 +2291,11 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '2연상']</t>
+          <t>['반도체', '산단', '주가']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10120</v>
+        <v>10280</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.60%</t>
+          <t>-1.06%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G21" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="H21" t="n">
         <v>5.75</v>
@@ -2358,7 +2358,7 @@
         <v>5.7</v>
       </c>
       <c r="O21" t="n">
-        <v>19846267585</v>
+        <v>20283509785</v>
       </c>
       <c r="P21" t="n">
         <v>15640</v>
@@ -2367,7 +2367,7 @@
         <v>5470</v>
       </c>
       <c r="R21" t="n">
-        <v>-120000</v>
+        <v>-122000</v>
       </c>
       <c r="S21" t="n">
         <v>-2000</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5500</v>
+        <v>5510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-3.50%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2421,10 +2421,10 @@
         <v>84</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G22" t="n">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="H22" t="n">
         <v>4.81</v>
@@ -2450,7 +2450,7 @@
         <v>4.39</v>
       </c>
       <c r="O22" t="n">
-        <v>20732557755</v>
+        <v>21326612740</v>
       </c>
       <c r="P22" t="n">
         <v>10480</v>
@@ -2459,7 +2459,7 @@
         <v>3150</v>
       </c>
       <c r="R22" t="n">
-        <v>-432000</v>
+        <v>-473000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
